--- a/documents/3_test/02_integration/結合テスト仕様書.xlsx
+++ b/documents/3_test/02_integration/結合テスト仕様書.xlsx
@@ -21,7 +21,6 @@
     <sheet name="IT-11" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="IT-12" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="IT-13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="IT-14" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,23 +39,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Yu Gothic"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +103,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,14 +469,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="8.600000000000001" customWidth="1" min="4" max="4"/>
-    <col width="6.4" customWidth="1" min="5" max="5"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="8.800000000000001" customWidth="1" min="4" max="4"/>
+    <col width="6.600000000000001" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,74 +565,110 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 結合テストでは「画面をまたぐデータ連携」「外部API連携」「E2Eフロー」を確認する</t>
+          <t xml:space="preserve">  - 結合テストでは「画面をまたぐデータ連携」「外部API連携」「E2Eフロー」を確認する</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 単画面内で完結するバリデーション・UI制御は単体テスト（01_unit/機能一覧）でカバー済みのため、結合テストには含めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - 単画面内で完結するバリデーション・UI制御は単体テスト（01_unit/機能一覧）でカバー済みのため、結合テストには含めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>テストシナリオ一覧</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>テストシナリオ一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>エンドユーザー系</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>テストID</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>シナリオ名</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>主な結合点</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>エンドユーザー系</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>IT-01</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>新規会員登録〜原稿一覧表示</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>新規登録 → メール認証 → 企業情報保存 → 初期行事自動作成 → 原稿一覧遷移</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>テストID</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>シナリオ名</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>主な結合点</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>IT-02</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ログイン〜画面遷移分岐</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>認証API → ロール / 登録状態による遷移先分岐 → 全保護画面アクセス制御</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>IT-01</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>新規会員登録〜原稿一覧表示</t>
+          <t>パスワード再設定フロー</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>新規登録 → メール認証 → 企業情報保存 → 初期行事自動作成 → 原稿一覧遷移</t>
+          <t>PW再設定メール送信 → リンク遷移 → PW更新 → 新PWでログイン</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -641,17 +677,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>IT-02</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ログイン〜画面遷移分岐</t>
+          <t>アカウント情報変更</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>認証API → ロール / 登録状態による遷移先分岐 → 全保護画面アクセス制御</t>
+          <t>PW照合 → PW更新 / メアド認証メール → 認証リンク → メアド更新 → 新認証情報でログイン</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -660,17 +696,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>IT-03</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>パスワード再設定フロー</t>
+          <t>企業情報登録〜行事情報初期化</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>PW再設定メール送信 → リンク遷移 → PW更新 → 新PWでログイン</t>
+          <t>企業情報保存 → 初期行事自動作成 → 原稿一覧反映</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -679,17 +715,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>IT-04</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>アカウント情報変更</t>
+          <t>行事新規作成〜原稿生成〜ダウンロード</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>PW照合 → PW更新 / メアド認証メール → 認証リンク → メアド更新 → 新認証情報でログイン</t>
+          <t>行事保存 → 評価 → POST /generated-images → ポーリング → GET /files/{fileKey}/url → DL</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
@@ -698,17 +734,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>IT-05</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>企業情報登録〜行事情報初期化</t>
+          <t>行事編集〜原稿再生成</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>企業情報保存 → 初期行事自動作成 → 原稿一覧反映</t>
+          <t>行事更新/複製/削除 → 再生成API → 画面反映</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
@@ -717,17 +753,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>IT-06</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>行事新規作成〜原稿生成〜ダウンロード</t>
+          <t>共通印刷物ダウンロード</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>行事保存 → 評価 → POST /generated-images → ポーリング → GET /files/{fileKey}/url → DL</t>
+          <t>業界別グループ表示制御 → 印刷物一覧 → GET /files/{fileKey}/url → DL</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -736,265 +772,208 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>IT-07</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>行事編集〜原稿再生成</t>
+          <t>年度切り替え〜一覧表示更新</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>行事更新/複製/削除 → 再生成API → 画面反映</t>
+          <t>サイドメニュー年度変更 → 各一覧再取得 → ロール別メニュー表示 → 各画面遷移</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>IT-08</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>共通印刷物ダウンロード</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>業界別グループ表示制御 → 印刷物一覧 → GET /files/{fileKey}/url → DL</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-    </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>IT-09</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>ノベルティ閲覧</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>サイドメニュー → 業界小分類に紐づくPDF別タブ表示</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>管理者系</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>テストID</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>シナリオ名</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>主な結合点</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>IT-10</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>年度切り替え〜一覧表示更新</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>サイドメニュー年度変更 → 各一覧再取得 → ロール別メニュー表示 → 各画面遷移</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>業界・行事テンプレート CRUD</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>業界CRUD → テンプレートCRUD → エンドユーザー側反映</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+    </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>管理者系</t>
-        </is>
-      </c>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>IT-11</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>デザインテンプレート CRUD</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>GET /source-image-groups → サイズ別画像取得 → テンプレCRUD → 行事テンプレート側反映</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>テストID</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>シナリオ名</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>主な結合点</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>IT-12</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>評価ログ CSV ダウンロード</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>年度/月絞り込み → JavaScript CSV生成（DLログ/評価ログ） → DL</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>IT-11</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>業界・行事テンプレート CRUD</t>
+          <t>共通印刷物管理 CRUD</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>業界CRUD → テンプレートCRUD → エンドユーザー側反映</t>
+          <t>グループCRUD（業界紐づけ） → GET /common-print-groups → エンドユーザー側反映</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>IT-12</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>デザインテンプレート CRUD</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>GET /source-image-groups → サイズ別画像取得 → テンプレCRUD → 行事テンプレート側反映</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>IT-13</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>評価ログ CSV ダウンロード</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>年度/月絞り込み → JavaScript CSV生成（DLログ/評価ログ） → DL</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>IT-14</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>共通印刷物管理 CRUD</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>グループCRUD（業界紐づけ） → GET /common-print-groups → エンドユーザー側反映</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>画面遷移の連鎖</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>操作の結果として正しい画面へ遷移すること</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>画面間のデータ連携</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>保存したデータが次画面・次回アクセス時に正しく表示されること</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>観点</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>外部API連携</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Brother APIのリクエスト・レスポンスが正しく処理されること</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>画面遷移の連鎖</t>
+          <t>ロール / 認証状態による制御</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>操作の結果として正しい画面へ遷移すること</t>
+          <t>認証状態・ロールに応じてアクセス制御が正しく機能すること</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>画面間のデータ連携</t>
+          <t>管理者→エンドユーザー反映</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>保存したデータが次画面・次回アクセス時に正しく表示されること</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>外部API連携</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Brother APIのリクエスト・レスポンスが正しく処理されること</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>ロール / 認証状態による制御</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>認証状態・ロールに応じてアクセス制御が正しく機能すること</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>管理者→エンドユーザー反映</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>管理者が作成・更新したデータがエンドユーザー側に正しく反映されること</t>
         </is>
@@ -1011,23 +990,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="15.2" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="49.50000000000001" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IT-09 ノベルティ閲覧</t>
+          <t>IT-09 年度切り替え〜一覧表示更新</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1038,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ノベルティ閲覧</t>
+          <t>年度切り替え〜一覧表示更新</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1050,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>サイドメニュー → ノベルティ（別タブPDF表示）</t>
+          <t>サイドメニュー（年度切り替え） → 各一覧画面</t>
         </is>
       </c>
     </row>
@@ -1102,22 +1081,28 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- サイドメニュー選択 → ユーザーの業界小分類に紐づくPDFが別タブ表示</t>
+          <t xml:space="preserve">  - サイドメニュー年度ドロップダウン変更 → 各一覧画面のデータ再取得 → 表示切り替え</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 業界小分類によるPDF出し分け</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - ロールに応じたサイドメニュー項目の出し分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - サイドメニューから各画面への遷移</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>テストケース</t>
+          <t>IT-09-01 年度切り替え動作確認</t>
         </is>
       </c>
     </row>
@@ -1171,22 +1156,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ノベルティ選択</t>
+          <t>年度切り替え（行事一覧）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>サイドメニューで「ノベルティ」を選択する</t>
+          <t>行事一覧表示中に年度ドロップダウンを変更する</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ユーザーの業界小分類に紐づくPDFが別タブで表示される</t>
+          <t>選択した年度の行事一覧が再取得され表示される</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -1201,27 +1186,337 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>業界小分類によるPDF出し分け</t>
+          <t>年度切り替え（共通印刷物）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>異なる業界小分類のユーザーでノベルティを選択する</t>
+          <t>共通印刷物一覧表示中に年度ドロップダウンを変更する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>それぞれの業界小分類に対応するPDFが表示される</t>
+          <t>選択した年度に対応する一覧が再取得されて表示される</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>IT-09-02 サイドメニュー遷移確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>行事一覧への遷移</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>サイドメニューで「行事一覧」を選択する</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>「原稿_一覧 / 詳細」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>共通印刷物への遷移</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>「共通印刷物」を選択する</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>「共通印刷物_一覧 / 詳細」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>企業情報への遷移</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>「企業情報」を選択する</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>「企業情報」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>アカウント情報への遷移</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>「アカウント情報」を選択する</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>「アカウント情報」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ログアウト</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>「ログアウト」を選択する</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ログアウトされ「ログイン」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>IT-09-03 ロール別メニュー表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>エンドユーザーのメニュー</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>role=エンドユーザーでログインする</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>行事一覧・共通印刷物・ノベルティ・企業情報・アカウント情報・ログアウトが表示される</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>管理者のメニュー</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>role=管理者でログインする</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>ログ管理・業界/行事テンプレ・デザインテンプレ・共通印刷物・ログアウトが表示される</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1234,23 +1529,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="49.3" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="52.8" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IT-10 年度切り替え〜一覧表示更新</t>
+          <t>IT-10 業界 / 行事テンプレート CRUD</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1577,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>年度切り替え〜一覧表示更新</t>
+          <t>業界 / 行事テンプレート CRUD</t>
         </is>
       </c>
     </row>
@@ -1294,60 +1589,71 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>サイドメニュー（年度切り替え） → 各一覧画面</t>
+          <t>業界 / 行事テンプレート管理（`/admin_e-temp`）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
+          <t>対象ユーザー</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>管理者のみ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>結合確認ポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>- サイドメニュー年度ドロップダウン変更 → 各一覧画面のデータ再取得 → 表示切り替え</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- ロールに応じたサイドメニュー項目の出し分け</t>
+          <t xml:space="preserve">  - 業界CRUD → 行事テンプレートCRUD → エンドユーザー側への反映</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>- サイドメニューから各画面への遷移</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t xml:space="preserve">  - 業界大分類・小分類の階層連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - デザインテンプレート選択（IT-11で作成したものが選択肢に表示される）</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IT-10-01 年度切り替え動作確認</t>
+          <t>IT-10-01 業界 CRUD〜階層連動</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1707,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>年度切り替え（行事一覧）</t>
+          <t>業界大分類作成</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>行事一覧表示中に年度ドロップダウンを変更する</t>
+          <t>業界大分類を新規作成する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1416,7 +1722,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>選択した年度の行事一覧が再取得され表示される</t>
+          <t>業界が作成され、配下に業界小分類 新規追加ボタンが表示される</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -1431,12 +1737,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>年度切り替え（共通印刷物）</t>
+          <t>業界小分類作成</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>共通印刷物一覧表示中に年度ドロップダウンを変更する</t>
+          <t>業界小分類を新規作成する</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1446,147 +1752,147 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>選択した年度に対応する一覧が再取得されて表示される</t>
+          <t>業界大分類の配下に業界小分類が追加される</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>業界編集</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>業界名を変更して保存する</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>一覧の表示が更新される</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>IT-10-02 サイドメニュー遷移確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>業界削除</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>削除を実行する</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>一覧から非表示になる</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>IT-10-02 行事テンプレート CRUD〜エンドユーザー反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>操作ステップ</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>操作内容</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>確認システム</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>実行者</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>実行日</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>行事一覧への遷移</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>サイドメニューで「行事一覧」を選択する</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>「原稿_一覧 / 詳細」画面へ遷移する</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>共通印刷物への遷移</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>「共通印刷物」を選択する</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>「共通印刷物_一覧 / 詳細」画面へ遷移する</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>企業情報への遷移</t>
+          <t>テンプレート作成</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>「企業情報」を選択する</t>
+          <t>開催月・行事名・デザインテンプレートx3を設定して保存する</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>「企業情報」画面へ遷移する</t>
+          <t>テンプレートが作成され一覧に追加される</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -1596,17 +1902,17 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>アカウント情報への遷移</t>
+          <t>初期表示テンプレ切り替え</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>「アカウント情報」を選択する</t>
+          <t>初期表示テンプレの切り替えボタンを操作する</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1616,7 +1922,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>「アカウント情報」画面へ遷移する</t>
+          <t>true/falseが切り替わる</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -1626,17 +1932,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ログアウト</t>
+          <t>テンプレート編集</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>「ログアウト」を選択する</t>
+          <t>内容を変更して保存する</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1646,122 +1952,72 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ログアウトされ「ログイン」画面へ遷移する</t>
+          <t>テンプレートが更新される</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>テンプレート削除</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>削除を実行する</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>一覧から非表示になる</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>IT-10-03 ロール別メニュー表示確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>エンドユーザーのメニュー</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>role=エンドユーザーでログインする</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>エンドユーザー側反映確認</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>エンドユーザーでログインし行事新規作成ポップアップを開く</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>フロント</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>行事一覧・共通印刷物・ノベルティ・企業情報・アカウント情報・ログアウトが表示される</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>管理者のメニュー</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>role=管理者でログインする</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>ログ管理・業界/行事テンプレ・デザインテンプレ・共通印刷物・ログアウトが表示される</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>管理者が作成したテンプレートが選択肢に表示される</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1774,23 +2030,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="49.50000000000001" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IT-11 業界 / 行事テンプレート CRUD</t>
+          <t>IT-11 デザインテンプレート CRUD</t>
         </is>
       </c>
     </row>
@@ -1822,7 +2078,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>業界 / 行事テンプレート CRUD</t>
+          <t>デザインテンプレート CRUD</t>
         </is>
       </c>
     </row>
@@ -1834,7 +2090,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>業界 / 行事テンプレート管理（`/admin_e-temp`）</t>
+          <t>デザインテンプレート管理（`/admin_d-temp`）</t>
         </is>
       </c>
     </row>
@@ -1877,98 +2133,150 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 業界CRUD → 行事テンプレートCRUD → エンドユーザー側への反映</t>
+          <t xml:space="preserve">  - Brother API連携（GET /source-image-groups → GET /source-image-groups/{id}/source-images）でソース画像を取得</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>- 業界大分類・小分類の階層連動</t>
+          <t xml:space="preserve">  - テンプレートCRUD → 行事テンプレート側（IT-10）の選択肢への反映</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>- デザインテンプレート選択（IT-12で作成したものが選択肢に表示される）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IT-11-01 テンプレート新規作成〜Brother API連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>IT-11-01 業界 CRUD〜階層連動</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ソースイメージグループ取得</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>API呼び出しボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>フロント → 外部API</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>GET /source-image-groups が呼ばれ、サムネイル一覧がポップアップ表示される</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>グループ選択〜サイズ別画像取得</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>サムネイルを選択する</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>フロント → 外部API</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>GET /source-image-groups/{id}/source-images が呼ばれ、サイズ別サムネイルが表示される</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>業界大分類作成</t>
+          <t>API接続エラー時</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>業界大分類を新規作成する</t>
+          <t>API呼び出しが失敗する場合</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>業界が作成され、配下に業界小分類 新規追加ボタンが表示される</t>
+          <t>アラートが表示される</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -1978,17 +2286,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>業界小分類作成</t>
+          <t>テンプレート保存</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>業界小分類を新規作成する</t>
+          <t>開催月・テンプレート名を入力して保存する</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1998,272 +2306,202 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>業界大分類の配下に業界小分類が追加される</t>
+          <t>テンプレートが作成され一覧に追加される</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>業界編集</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>業界名を変更して保存する</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>IT-11-02 テンプレート編集・削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>テンプレート編集・保存</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ソースイメージやテンプレート名を変更して保存する</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>フロント → バック</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>一覧の表示が更新される</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>業界削除</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>テンプレートが更新され一覧に反映される</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>テンプレート削除</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>削除を実行する</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>フロント → バック</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>一覧から非表示になる</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>IT-11-02 行事テンプレート CRUD〜エンドユーザー反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>IT-11-03 他画面への反映確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>操作ステップ</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>操作内容</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>確認システム</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>実行者</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>実行日</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>テンプレート作成</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>開催月・行事名・デザインテンプレートx3を設定して保存する</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>テンプレートが作成され一覧に追加される</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>初期表示テンプレ切り替え</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>初期表示テンプレの切り替えボタンを操作する</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>true/falseが切り替わる</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>テンプレート編集</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>内容を変更して保存する</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>テンプレートが更新される</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>テンプレート削除</t>
+          <t>行事テンプレート側への反映</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>削除を実行する</t>
+          <t>業界/行事テンプレート管理でデザインテンプレート選択欄を確認する</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>一覧から非表示になる</t>
+          <t>作成したデザインテンプレートが選択肢に表示される</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>エンドユーザー側反映確認</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>エンドユーザーでログインし行事新規作成ポップアップを開く</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>管理者が作成したテンプレートが選択肢に表示される</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2276,23 +2514,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="49.3" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="21.8" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="46.2" customWidth="1" min="3" max="3"/>
+    <col width="15.4" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IT-12 デザインテンプレート CRUD</t>
+          <t>IT-12 評価ログ CSV ダウンロード</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2562,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>デザインテンプレート CRUD</t>
+          <t>評価ログ CSV ダウンロード</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2574,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>デザインテンプレート管理（`/admin_d-temp`）</t>
+          <t>評価ログ管理（`/admin_log`）</t>
         </is>
       </c>
     </row>
@@ -2379,22 +2617,28 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- Brother API連携（GET /source-image-groups → GET /source-image-groups/{id}/source-images）でソース画像を取得</t>
+          <t xml:space="preserve">  - ログ管理画面 → 年度/月絞り込み → JavaScript CSV生成 → ダウンロード</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>- テンプレートCRUD → 行事テンプレート側（IT-11）の選択肢への反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t xml:space="preserve">  - ダウンロードログCSVと評価ログCSVの2種類が正しく生成されること</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - リレーション先からの値取得が正しいこと</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IT-12-01 テンプレート新規作成〜Brother API連携</t>
+          <t>IT-12-01 ダウンロードログCSV</t>
         </is>
       </c>
     </row>
@@ -2448,22 +2692,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ソースイメージグループ取得</t>
+          <t>ダウンロードログCSV生成・DL</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>API呼び出しボタンを押下する</t>
+          <t>対象月のダウンロードログボタンを押下する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>フロント → 外部API</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>GET /source-image-groups が呼ばれ、サムネイル一覧がポップアップ表示される</t>
+          <t>JavaScriptでCSVが生成されローカルにダウンロードされる</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -2478,277 +2722,137 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>グループ選択〜サイズ別画像取得</t>
+          <t>CSVカラム・リレーション確認</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>サムネイルを選択する</t>
+          <t>DLしたCSVを確認する</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>フロント → 外部API</t>
+          <t>手動</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>GET /source-image-groups/{id}/source-images が呼ばれ、サイズ別サムネイルが表示される</t>
+          <t>ログ草案記載のカラムが含まれ、リレーション先から正しく値が取得されている</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>API接続エラー時</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>API呼び出しが失敗する場合</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>IT-12-02 評価ログCSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>評価ログCSV生成・DL</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>対象月の評価ログボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>フロント</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>アラートが表示される</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>テンプレート保存</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>開催月・テンプレート名を入力して保存する</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>テンプレートが作成され一覧に追加される</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>IT-12-02 テンプレート編集・削除</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>JavaScriptでCSVが生成されローカルにダウンロードされる</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>テンプレート編集・保存</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>ソースイメージやテンプレート名を変更して保存する</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>テンプレートが更新され一覧に反映される</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>テンプレート削除</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>削除を実行する</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>一覧から非表示になる</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>IT-12-03 他画面への反映確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>行事テンプレート側への反映</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>業界/行事テンプレート管理でデザインテンプレート選択欄を確認する</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>作成したデザインテンプレートが選択肢に表示される</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>CSVカラム・リレーション確認</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>DLしたCSVを確認する</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>手動</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ログ草案記載のカラムが含まれ、リレーション先から正しく値が取得されている</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2761,23 +2865,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="32.8" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="15.2" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="38.5" customWidth="1" min="2" max="2"/>
+    <col width="52.8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IT-13 評価ログ CSV ダウンロード</t>
+          <t>IT-13 共通印刷物管理 CRUD</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2913,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>評価ログ CSV ダウンロード</t>
+          <t>共通印刷物管理 CRUD</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2925,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>評価ログ管理（`/admin_log`）</t>
+          <t>共通印刷物管理（`/admin_prints`）</t>
         </is>
       </c>
     </row>
@@ -2864,98 +2968,127 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- ログ管理画面 → 年度/月絞り込み → JavaScript CSV生成 → ダウンロード</t>
+          <t xml:space="preserve">  - グループCRUD → 業界紐づけパターンによる配置（全業界共通 / 業界大分類共通 / 業界小分類配下）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>- ダウンロードログCSVと評価ログCSVの2種類が正しく生成されること</t>
+          <t xml:space="preserve">  - Brother API連携（GET /common-print-groups → GET /common-print-groups/{id}）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>- リレーション先からの値取得が正しいこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t xml:space="preserve">  - エンドユーザー側（IT-07）への反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>IT-13-01 グループ新規作成〜業界紐づけ</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>IT-13-01 ダウンロードログCSV</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>印刷物取得（API呼び出し）</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>API呼び出しボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>フロント → 外部API</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>GET /common-print-groups が呼ばれ、グループ一覧がポップアップ表示される</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ダウンロードログCSV生成・DL</t>
+          <t>グループ選択〜印刷物取得</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>対象月のダウンロードログボタンを押下する</t>
+          <t>グループを選択する</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → 外部API</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>JavaScriptでCSVが生成されローカルにダウンロードされる</t>
+          <t>GET /common-print-groups/{id} が呼ばれ、印刷物一覧が表示される</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -2965,409 +3098,57 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CSVカラム・リレーション確認</t>
+          <t>API接続エラー時</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>DLしたCSVを確認する</t>
+          <t>API呼び出しが失敗する場合</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>手動</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ログ草案記載のカラムが含まれ、リレーション先から正しく値が取得されている</t>
+          <t>アラートが表示される</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>IT-13-02 評価ログCSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>評価ログCSV生成・DL</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>対象月の評価ログボタンを押下する</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>JavaScriptでCSVが生成されローカルにダウンロードされる</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>CSVカラム・リレーション確認</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>DLしたCSVを確認する</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>手動</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>ログ草案記載のカラムが含まれ、リレーション先から正しく値が取得されている</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="38.3" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="21.8" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>IT-14 共通印刷物管理 CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>シナリオ名</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>共通印刷物管理 CRUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>対象画面</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>共通印刷物管理（`/admin_prints`）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>対象ユーザー</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>管理者のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>実施日</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>結合確認ポイント</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>- グループCRUD → 業界紐づけパターンによる配置（全業界共通 / 業界大分類共通 / 業界小分類配下）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>- Brother API連携（GET /common-print-groups → GET /common-print-groups/{id}）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>- エンドユーザー側（IT-08）への反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>IT-14-01 グループ新規作成〜業界紐づけ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>印刷物取得（API呼び出し）</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>API呼び出しボタンを押下する</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>フロント → 外部API</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>GET /common-print-groups が呼ばれ、グループ一覧がポップアップ表示される</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>グループ選択〜印刷物取得</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>グループを選択する</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>フロント → 外部API</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>GET /common-print-groups/{id} が呼ばれ、印刷物一覧が表示される</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-    </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>API接続エラー時</t>
+          <t>保存（業界未選択=全業界共通）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>API呼び出しが失敗する場合</t>
+          <t>業界を未選択のまま保存する</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>アラートが表示される</t>
+          <t>グループが作成され全業界共通配下に表示される</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -3377,17 +3158,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>保存（業界未選択=全業界共通）</t>
+          <t>保存（業界大分類のみ選択）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>業界を未選択のまま保存する</t>
+          <t>業界大分類のみ選択して保存する</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3397,7 +3178,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>グループが作成され全業界共通配下に表示される</t>
+          <t>グループが作成され業界大分類共通配下に表示される</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -3407,17 +3188,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>保存（業界大分類のみ選択）</t>
+          <t>保存（業界大分類・小分類選択）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>業界大分類のみ選択して保存する</t>
+          <t>業界大分類・小分類を選択して保存する</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -3427,107 +3208,107 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>グループが作成され業界大分類共通配下に表示される</t>
+          <t>グループが作成され業界小分類配下に表示される</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>保存（業界大分類・小分類選択）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>業界大分類・小分類を選択して保存する</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>IT-13-02 グループ編集・削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>グループ編集・保存</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>グループ名や業界選択を変更して保存する</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>フロント → バック</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>グループが作成され業界小分類配下に表示される</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>IT-14-02 グループ編集・削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>更新され一覧に反映される</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>グループ編集・保存</t>
+          <t>グループ削除</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>グループ名や業界選択を変更して保存する</t>
+          <t>削除を実行する</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -3537,122 +3318,92 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>更新され一覧に反映される</t>
+          <t>一覧から非表示になる</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>グループ削除</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>削除を実行する</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>一覧から非表示になる</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>IT-13-03 エンドユーザー側反映確認</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>IT-14-03 エンドユーザー側反映確認</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>エンドユーザー側表示確認</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>エンドユーザーでログインし共通印刷物画面を開く</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>フロント</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>管理者が作成したグループ・印刷物が業界に応じて表示される</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3665,17 +3416,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3756,91 +3507,120 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 新規登録 → メール認証 → 企業情報保存 → 初期行事自動作成 → 原稿一覧遷移の一連フロー</t>
+          <t xml:space="preserve">  - 新規登録 → メール認証 → 企業情報保存 → 初期行事自動作成 → 原稿一覧遷移の一連フロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 画面間のデータ引き継ぎ（ユーザー情報 → 企業情報 → 行事情報）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - 画面間のデータ引き継ぎ（ユーザー情報 → 企業情報 → 行事情報）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IT-01-01 新規登録〜認証メール送信〜企業情報〜原稿一覧</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IT-01-01 新規登録〜認証メール送信〜企業情報〜原稿一覧</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>新規登録画面でメアド・pw入力</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>未登録のメアドと有効なpwを入力して新規登録ボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>新規登録APIが呼ばれる</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>新規登録画面でメアド・pw入力</t>
+          <t>ユーザー・企業情報自動作成確認</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>未登録のメアドと有効なpwを入力して新規登録ボタンを押下する</t>
+          <t>（自動処理）</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>バック</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>新規登録APIが呼ばれる</t>
+          <t>ユーザー情報・企業情報がDBに作成され紐付けられる</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -3850,27 +3630,27 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ユーザー・企業情報自動作成確認</t>
+          <t>認証メール送信確認</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>（自動処理）</t>
+          <t>登録メアドを確認する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>バック</t>
+          <t>メールサーバー</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ユーザー情報・企業情報がDBに作成され紐付けられる</t>
+          <t>認証メールが届いている</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -3880,27 +3660,27 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>認証メール送信確認</t>
+          <t>認証リンクアクセス</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>登録メアドを確認する</t>
+          <t>届いた認証メールのリンクをクリックする</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>メールサーバー</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>認証メールが届いている</t>
+          <t>認証APIが呼ばれ、ログイン状態になる</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -3910,27 +3690,27 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>認証リンクアクセス</t>
+          <t>企業情報画面遷移確認</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>届いた認証メールのリンクをクリックする</t>
+          <t>画面を確認する</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>認証APIが呼ばれ、ログイン状態になる</t>
+          <t>企業情報=未登録のため「企業情報」画面へ遷移している</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -3940,27 +3720,27 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>企業情報画面遷移確認</t>
+          <t>企業情報入力・保存</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>画面を確認する</t>
+          <t>必須項目を入力して保存ボタンを押下する</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>企業情報=未登録のため「企業情報」画面へ遷移している</t>
+          <t>企業情報保存APIが呼ばれる</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -3970,27 +3750,27 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>企業情報入力・保存</t>
+          <t>初期行事情報の自動作成確認</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>必須項目を入力して保存ボタンを押下する</t>
+          <t>（自動処理）</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>バック</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>企業情報保存APIが呼ばれる</t>
+          <t>選択した業種に紐づく初期行事情報がDBに作成される</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -4000,252 +3780,222 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>初期行事情報の自動作成確認</t>
+          <t>原稿一覧遷移確認</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>（自動処理）</t>
+          <t>画面を確認する</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>選択した業種に紐づく初期行事情報がDBに作成される</t>
+          <t>「原稿_一覧 / 詳細」画面へ遷移し、初期行事が一覧に表示される</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>原稿一覧遷移確認</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>画面を確認する</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>「原稿_一覧 / 詳細」画面へ遷移し、初期行事が一覧に表示される</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>IT-01-02 メール重複時のフロー</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>IT-01-02 メール重複時のフロー</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>既存メアドで新規登録</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>登録済みのメアドで新規登録を実行する</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>アラートが表示され、登録が行われない</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>IT-01-03 認証メール再送信</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>操作ステップ</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>操作内容</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>確認システム</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>実行者</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>実行日</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>既存メアドで新規登録</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>登録済みのメアドで新規登録を実行する</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>再送信実行</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>認証メール送信済み画面で再送信ボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>フロント → バック</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>アラートが表示され、登録が行われない</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>IT-01-03 認証メール再送信</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>認証メールが再送信される</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>再送信実行</t>
+          <t>メール到達確認</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>認証メール送信済み画面で再送信ボタンを押下する</t>
+          <t>登録メアドを確認する</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>メールサーバー</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>認証メールが再送信される</t>
+          <t>認証メールが届いている</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>メール到達確認</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>登録メアドを確認する</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>メールサーバー</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>認証メールが届いている</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4258,17 +4008,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="32.8" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="35.2" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="52.8" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4349,71 +4099,100 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 認証API → ロール / 登録状態による遷移先分岐</t>
+          <t xml:space="preserve">  - 認証API → ロール / 登録状態による遷移先分岐</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 未ログイン・ロール不一致時の全保護画面アクセス制御</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - 未ログイン・ロール不一致時の全保護画面アクセス制御</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IT-02-01 ログイン成功〜遷移先分岐</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IT-02-01 ログイン成功〜遷移先分岐</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>メール認証済み・利用者・企業情報=未登録</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック → フロント</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>「企業情報」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -4423,7 +4202,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>メール認証済み・利用者・企業情報=未登録</t>
+          <t>メール認証済み・利用者・企業情報=登録済・年間行事=未登録</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -4433,7 +4212,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>「企業情報」画面へ遷移する</t>
+          <t>「原稿_一覧」画面へ遷移する</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -4443,7 +4222,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -4453,7 +4232,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>メール認証済み・利用者・企業情報=登録済・年間行事=未登録</t>
+          <t>メール認証済み・利用者・企業情報=登録済・年間行事=登録済</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -4473,7 +4252,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -4483,7 +4262,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>メール認証済み・利用者・企業情報=登録済・年間行事=登録済</t>
+          <t>メール未認証</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4493,7 +4272,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>「原稿_一覧」画面へ遷移する</t>
+          <t>認証メールが送信され、送信済み案内が表示される</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -4503,7 +4282,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -4513,7 +4292,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>メール未認証</t>
+          <t>ロール=管理者</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -4523,107 +4302,107 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>認証メールが送信され、送信済み案内が表示される</t>
+          <t>「ログ管理」画面へ遷移する</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ログイン</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>ロール=管理者</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック → フロント</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>「ログ管理」画面へ遷移する</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>IT-02-02 ログイン失敗</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>IT-02-02 ログイン失敗</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>誤ったpwでログイン</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>正しいメアド・誤ったpw</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>認証エラーアラートが表示される。画面遷移しない</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>誤ったpwでログイン</t>
+          <t>存在しないメアドでログイン</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>正しいメアド・誤ったpw</t>
+          <t>未登録のメアド</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4640,95 +4419,95 @@
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>存在しないメアドでログイン</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>未登録のメアド</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>認証エラーアラートが表示される。画面遷移しない</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>IT-02-03 未ログインでの保護画面アクセス</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>IT-02-03 未ログインでの保護画面アクセス</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>`/design` に直接アクセス</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>未ログイン状態</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>「ログイン」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>`/design` に直接アクセス</t>
+          <t>`/facility` に直接アクセス</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -4753,12 +4532,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>`/facility` に直接アクセス</t>
+          <t>`/mypage` に直接アクセス</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -4783,12 +4562,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>`/mypage` に直接アクセス</t>
+          <t>`/admin_log` に直接アクセス</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -4813,12 +4592,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>`/admin_log` に直接アクセス</t>
+          <t>`/admin_e-temp` に直接アクセス</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -4843,12 +4622,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>`/admin_e-temp` に直接アクセス</t>
+          <t>`/admin_d-temp` に直接アクセス</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -4873,12 +4652,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>`/admin_d-temp` に直接アクセス</t>
+          <t>`/admin_prints` に直接アクセス</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -4900,95 +4679,95 @@
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>`/admin_prints` に直接アクセス</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>未ログイン状態</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>IT-02-04 ロールによるアクセス制限</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>`/admin_log` に直接アクセス</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>ロール=エンドユーザーでログイン済み</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>フロント</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>「ログイン」画面へ遷移する</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>IT-02-04 ロールによるアクセス制限</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>`/admin_log` に直接アクセス</t>
+          <t>`/admin_e-temp` に直接アクセス</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -5013,12 +4792,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>`/admin_e-temp` に直接アクセス</t>
+          <t>`/admin_d-temp` に直接アクセス</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -5043,12 +4822,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>`/admin_d-temp` に直接アクセス</t>
+          <t>`/admin_prints` に直接アクセス</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -5069,36 +4848,6 @@
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>`/admin_prints` に直接アクセス</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>ロール=エンドユーザーでログイン済み</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>「ログイン」画面へ遷移する</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5111,17 +4860,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
+    <col width="50.6" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5202,91 +4951,120 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- PW再設定メール送信 → メールのリンク遷移 → PW更新 → 新PWでログイン成功の一連フロー</t>
+          <t xml:space="preserve">  - PW再設定メール送信 → メールのリンク遷移 → PW更新 → 新PWでログイン成功の一連フロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 再設定リンク以外からのアクセス制御</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - 再設定リンク以外からのアクセス制御</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IT-03-01 PW再設定メール送信〜PW更新〜ログイン</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IT-03-01 PW再設定メール送信〜PW更新〜ログイン</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PW再設定メール送信</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>登録済みのメアドを入力し送信ボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>PW再設定メールが送信され、送信完了案内が表示される</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PW再設定メール送信</t>
+          <t>メール到達確認</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>登録済みのメアドを入力し送信ボタンを押下する</t>
+          <t>入力したメアドを確認する</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>メールサーバー</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>PW再設定メールが送信され、送信完了案内が表示される</t>
+          <t>PW再設定リンク付きのメールが届いている</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -5296,27 +5074,27 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>メール到達確認</t>
+          <t>再設定リンクアクセス</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>入力したメアドを確認する</t>
+          <t>メールのリンクをクリックする</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>メールサーバー</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>PW再設定リンク付きのメールが届いている</t>
+          <t>パスワード再設定画面が表示される</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -5326,27 +5104,27 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>再設定リンクアクセス</t>
+          <t>PW再設定実行</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>メールのリンクをクリックする</t>
+          <t>新pwを入力して再設定ボタンを押下する</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>パスワード再設定画面が表示される</t>
+          <t>PW更新APIが呼ばれ、完了アラートが表示される</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -5356,27 +5134,27 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PW再設定実行</t>
+          <t>ログイン画面遷移</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>新pwを入力して再設定ボタンを押下する</t>
+          <t>アラートを閉じる</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>PW更新APIが呼ばれ、完了アラートが表示される</t>
+          <t>「ログイン」画面へ遷移する</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -5386,117 +5164,117 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ログイン画面遷移</t>
+          <t>新PWでのログイン確認</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>アラートを閉じる</t>
+          <t>更新したpwでログインする</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>「ログイン」画面へ遷移する</t>
+          <t>ログインに成功する</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>新PWでのログイン確認</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>更新したpwでログインする</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>ログインに成功する</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>IT-03-02 再設定画面のアクセス制御</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>IT-03-02 再設定画面のアクセス制御</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>`/reset_pw` に直接アクセス</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済み</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>「原稿_一覧 / 詳細」画面へ遷移する</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -5506,7 +5284,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>ログイン済み</t>
+          <t>未ログイン状態</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -5516,42 +5294,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>「原稿_一覧 / 詳細」画面へ遷移する</t>
+          <t>「ログイン」画面へ遷移する</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>`/reset_pw` に直接アクセス</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>未ログイン状態</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>「ログイン」画面へ遷移する</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5564,17 +5312,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
+    <col width="50.6" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5655,81 +5403,110 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- PW変更: 旧PW照合API → PW更新API → 新PWでログイン確認</t>
+          <t xml:space="preserve">  - PW変更: 旧PW照合API → PW更新API → 新PWでログイン確認</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- メアド変更: 認証メール送信 → 認証リンク（有効期限あり） → メアド更新 → 新メアドでログイン確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - メアド変更: 認証メール送信 → 認証リンク（有効期限あり） → メアド更新 → 新メアドでログイン確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IT-04-01 パスワード変更フロー</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IT-04-01 パスワード変更フロー</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PW変更実行</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>正しい旧pw・一致した新pwを入力して保存する</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>PW更新APIが呼ばれ、パスワードが変更される</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PW変更実行</t>
+          <t>旧pw誤りの場合</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>正しい旧pw・一致した新pwを入力して保存する</t>
+          <t>誤った旧pwで変更を実行する</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -5739,7 +5516,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>PW更新APIが呼ばれ、パスワードが変更される</t>
+          <t>旧pw照合APIがエラーを返し、アラートが表示される</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -5749,17 +5526,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>旧pw誤りの場合</t>
+          <t>新PWでのログイン確認</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>誤った旧pwで変更を実行する</t>
+          <t>ログアウト後に変更したpwでログインする</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -5769,107 +5546,107 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>旧pw照合APIがエラーを返し、アラートが表示される</t>
+          <t>ログインに成功する</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>新PWでのログイン確認</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>ログアウト後に変更したpwでログインする</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>IT-04-02 メールアドレス変更フロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>メアド変更実行</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>未登録の新メアドと正しいpwを入力して変更する</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>フロント → バック</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>ログインに成功する</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>IT-04-02 メールアドレス変更フロー</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>新メアド宛に認証メールが送信される</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>メアド変更実行</t>
+          <t>既存メアドで変更</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>未登録の新メアドと正しいpwを入力して変更する</t>
+          <t>登録済みのメアドで変更を実行する</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -5879,7 +5656,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>新メアド宛に認証メールが送信される</t>
+          <t>重複チェックAPIがエラーを返し、アラートが表示される</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -5889,27 +5666,27 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>既存メアドで変更</t>
+          <t>認証リンク（有効期限内）をクリック</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>登録済みのメアドで変更を実行する</t>
+          <t>届いた認証メールのリンクをクリックする</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>バック</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>重複チェックAPIがエラーを返し、アラートが表示される</t>
+          <t>メールアドレスが更新される</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
@@ -5919,27 +5696,27 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>認証リンク（有効期限内）をクリック</t>
+          <t>認証リンク（有効期限切れ）をクリック</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>届いた認証メールのリンクをクリックする</t>
+          <t>期限切れの認証リンクをクリックする</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>メールアドレスが更新される</t>
+          <t>エラーアラートが表示される。メアドは更新されない</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -5949,62 +5726,32 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>認証リンク（有効期限切れ）をクリック</t>
+          <t>新メアドでのログイン確認</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>期限切れの認証リンクをクリックする</t>
+          <t>ログアウト後に変更したメアドでログインする</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → バック</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>エラーアラートが表示される。メアドは更新されない</t>
+          <t>ログインに成功する</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>新メアドでのログイン確認</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>ログアウト後に変更したメアドでログインする</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>ログインに成功する</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6017,17 +5764,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="40.5" customWidth="1" min="2" max="2"/>
-    <col width="43.8" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="40.7" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6108,91 +5855,120 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 企業情報保存 → 初期行事情報自動作成 → 原稿一覧への反映</t>
+          <t xml:space="preserve">  - 企業情報保存 → 初期行事情報自動作成 → 原稿一覧への反映</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 企業情報編集 → 再表示時にDBの値が反映されること</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - 企業情報編集 → 再表示時にDBの値が反映されること</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IT-05-01 企業情報新規登録〜初期行事作成</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IT-05-01 企業情報新規登録〜初期行事作成</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>企業情報入力・保存</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>必須項目を入力して保存ボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>企業情報保存APIが呼ばれ、ユーザーに紐付けられる</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>企業情報入力・保存</t>
+          <t>初期行事情報の自動作成確認</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>必須項目を入力して保存ボタンを押下する</t>
+          <t>（自動処理）</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>バック</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>企業情報保存APIが呼ばれ、ユーザーに紐付けられる</t>
+          <t>選択した業種に紐づく初期行事情報がDBに作成される</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -6202,127 +5978,127 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>初期行事情報の自動作成確認</t>
+          <t>原稿一覧遷移・反映確認</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>（自動処理）</t>
+          <t>画面を確認する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>選択した業種に紐づく初期行事情報がDBに作成される</t>
+          <t>「原稿_一覧 / 詳細」画面へ遷移し、初期行事が一覧に表示される</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>原稿一覧遷移・反映確認</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>画面を確認する</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>「原稿_一覧 / 詳細」画面へ遷移し、初期行事が一覧に表示される</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>IT-05-02 企業情報編集〜再表示</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>IT-05-02 企業情報編集〜再表示</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>企業情報編集・保存</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>企業名などを変更して保存する</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>企業情報更新APIが呼ばれる</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>企業情報編集・保存</t>
+          <t>変更の反映確認</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>企業名などを変更して保存する</t>
+          <t>企業情報画面を再表示する</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -6332,42 +6108,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>企業情報更新APIが呼ばれる</t>
+          <t>変更した内容がフィールドに反映されている</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>変更の反映確認</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>企業情報画面を再表示する</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>フロント → バック</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>変更した内容がフィールドに反映されている</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6380,17 +6126,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="21.8" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6471,88 +6217,117 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 行事保存 → デザイン評価 → Brother API原稿生成 → ポーリング → 原稿表示 → ダウンロードのE2Eフロー</t>
+          <t xml:space="preserve">  - 行事保存 → デザイン評価 → Brother API原稿生成 → ポーリング → 原稿表示 → ダウンロードのE2Eフロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- Brother API連携（POST /generated-images → GET /generated-images/{id} → GET /files/{fileKey}/url）</t>
+          <t xml:space="preserve">  - Brother API連携（POST /generated-images → GET /generated-images/{id} → GET /files/{fileKey}/url）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>- 生成対象サイズ: A3・A4・長尺縦・長尺横・ハガキ・封筒（A4便箋はAPI対象外）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t xml:space="preserve">  - 生成対象サイズ: A3・A4・長尺縦・長尺横・ハガキ・封筒（A4便箋はAPI対象外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IT-06-01 行事新規作成〜原稿生成</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>IT-06-01 行事新規作成〜原稿生成</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>行事新規作成・保存</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>必須項目（開催月・行事名・開催期間）を入力して保存する</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>行事保存APIが呼ばれ、新規行事レコードが作成される</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>行事新規作成・保存</t>
+          <t>デザイン評価</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>必須項目（開催月・行事名・開催期間）を入力して保存する</t>
+          <t>3種のデザインテンプレートを評価する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -6562,7 +6337,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>行事保存APIが呼ばれ、新規行事レコードが作成される</t>
+          <t>評価が保存される</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -6572,27 +6347,27 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>デザイン評価</t>
+          <t>原稿生成実行</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>3種のデザインテンプレートを評価する</t>
+          <t>生成ボタンを押下する</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント → 外部API</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>評価が保存される</t>
+          <t>各サイズごとにPOST /generated-imagesが呼ばれる（6回）</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -6602,17 +6377,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>原稿生成実行</t>
+          <t>ポーリング〜生成完了</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>生成ボタンを押下する</t>
+          <t>（自動処理）</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -6622,7 +6397,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>各サイズごとにPOST /generated-imagesが呼ばれる（6回）</t>
+          <t>GET /generated-images/{id} でポーリングされ、status=COMPLETEDで完了</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -6632,27 +6407,27 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ポーリング〜生成完了</t>
+          <t>原稿表示確認</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>（自動処理）</t>
+          <t>画面を確認する</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>フロント → 外部API</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>GET /generated-images/{id} でポーリングされ、status=COMPLETEDで完了</t>
+          <t>7サイズ分の原稿が一覧表示される</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -6662,17 +6437,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>原稿表示確認</t>
+          <t>生成失敗時の表示確認</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>画面を確認する</t>
+          <t>APIがエラーを返す場合</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -6682,262 +6457,232 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>7サイズ分の原稿が一覧表示される</t>
+          <t>取得失敗のアラートが表示される</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>生成失敗時の表示確認</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>APIがエラーを返す場合</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗のアラートが表示される</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>IT-06-02 原稿再生成</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>IT-06-02 原稿再生成</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>再生成実行</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>再生成ボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>フロント → 外部API</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>POST /generated-images/{id}/regenerate が呼ばれ、ポーリング後に画像が更新される</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>再生成実行</t>
+          <t>旧データの論理削除確認</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>再生成ボタンを押下する</t>
+          <t>（自動処理）</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>フロント → 外部API</t>
+          <t>バック</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>POST /generated-images/{id}/regenerate が呼ばれ、ポーリング後に画像が更新される</t>
+          <t>古いus_design_childが論理削除される</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>旧データの論理削除確認</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>（自動処理）</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>バック</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>古いus_design_childが論理削除される</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>IT-06-03 原稿ダウンロード</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>IT-06-03 原稿ダウンロード</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>全デザイン評価後にDL</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>全評価完了・DL期限内の状態でDLボタンを押下する</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>フロント → 外部API</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>GET /files/{fileKey}/url が呼ばれ、署名付きURLからダウンロードされる</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>全デザイン評価後にDL</t>
+          <t>ダウンロードAPI失敗時</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>全評価完了・DL期限内の状態でDLボタンを押下する</t>
+          <t>APIがエラーを返す場合</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>フロント → 外部API</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>GET /files/{fileKey}/url が呼ばれ、署名付きURLからダウンロードされる</t>
+          <t>アラートが表示される</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ダウンロードAPI失敗時</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>APIがエラーを返す場合</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>アラートが表示される</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6950,17 +6695,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20.7" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="53.90000000000001" customWidth="1" min="1" max="1"/>
+    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
+    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="20.9" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7041,353 +6786,352 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 行事更新 → 再生成API → 画面反映の一連フロー</t>
+          <t xml:space="preserve">  - 行事更新 → 再生成API → 画面反映の一連フロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- 行事複製 → 新規レコード作成 → 一覧反映</t>
+          <t xml:space="preserve">  - 行事複製 → 新規レコード作成 → 一覧反映</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>- 行事削除（論理削除） → 一覧から非表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t xml:space="preserve">  - 行事削除（論理削除） → 一覧から非表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IT-07-01 行事編集〜保存反映</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>IT-07-01 行事編集〜保存反映</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>行事編集・保存</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>編集ポップアップでフィールドを変更して保存する</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>行事更新APIが呼ばれ、行事レコードが更新される</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>行事編集・保存</t>
+          <t>更新内容の反映確認</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>編集ポップアップでフィールドを変更して保存する</t>
+          <t>行事一覧・詳細画面を確認する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>行事更新APIが呼ばれ、行事レコードが更新される</t>
+          <t>変更した内容が反映されている</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>更新内容の反映確認</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>行事一覧・詳細画面を確認する</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>変更した内容が反映されている</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>IT-07-02 行事複製</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>IT-07-02 行事複製</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>行事複製・保存</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>コピーアイコンを押下し、複製元の値が反映された状態で保存する</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>行事保存APIが呼ばれ、新規行事レコードが作成される</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>行事複製・保存</t>
+          <t>一覧反映確認</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>コピーアイコンを押下し、複製元の値が反映された状態で保存する</t>
+          <t>行事一覧を確認する</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>行事保存APIが呼ばれ、新規行事レコードが作成される</t>
+          <t>複製された行事が一覧に追加表示される</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>一覧反映確認</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>行事一覧を確認する</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>複製された行事が一覧に追加表示される</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>IT-07-03 行事削除</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>IT-07-03 行事削除</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>行事削除実行</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>削除ポップアップで削除を実行する</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>フロント → バック</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>削除APIが呼ばれ「削除Flag = true」で論理削除される</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>行事削除実行</t>
+          <t>一覧からの非表示確認</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>削除ポップアップで削除を実行する</t>
+          <t>行事一覧を確認する</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>フロント → バック</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>削除APIが呼ばれ「削除Flag = true」で論理削除される</t>
+          <t>削除した行事が一覧に表示されていない</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>一覧からの非表示確認</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>行事一覧を確認する</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>削除した行事が一覧に表示されていない</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7400,17 +7144,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="44.90000000000001" customWidth="1" min="2" max="2"/>
-    <col width="32.8" customWidth="1" min="3" max="3"/>
-    <col width="21.8" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="8.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
+    <col width="45.1" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
+    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7491,81 +7235,110 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>- 業界（大分類・小分類）によるグループ表示制御</t>
+          <t xml:space="preserve">  - 業界（大分類・小分類）によるグループ表示制御</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>- グループ選択 → 印刷物一覧表示 → Brother API（GET /files/{fileKey}/url）→ ダウンロード</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t xml:space="preserve">  - グループ選択 → 印刷物一覧表示 → Brother API（GET /files/{fileKey}/url）→ ダウンロード</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>テストケース</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>テストケース</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>操作ステップ</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>操作内容</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>確認システム</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>実行者</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>実行日</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>操作ステップ</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>操作内容</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>確認システム</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>期待値</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>実行者</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>実行日</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>業界別グループ表示確認</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>共通印刷物画面を開く</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ユーザーの業界に一致するグループと全業界横断グループが表示され、不一致のグループは表示されない</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>業界別グループ表示確認</t>
+          <t>グループ選択〜印刷物表示</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>共通印刷物画面を開く</t>
+          <t>グループを選択する</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -7575,7 +7348,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ユーザーの業界に一致するグループと全業界横断グループが表示され、不一致のグループは表示されない</t>
+          <t>グループに紐づく共通印刷物（画像・名前）が表示される</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -7585,27 +7358,27 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>グループ選択〜印刷物表示</t>
+          <t>ダウンロード実行</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>グループを選択する</t>
+          <t>ダウンロードボタンを押下する</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>フロント</t>
+          <t>フロント → 外部API</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>グループに紐づく共通印刷物（画像・名前）が表示される</t>
+          <t>GET /files/{fileKey}/url が呼ばれ、署名付きURLからローカルにダウンロードされる</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -7615,62 +7388,32 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ダウンロード実行</t>
+          <t>ダウンロードAPI失敗時</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ダウンロードボタンを押下する</t>
+          <t>APIがエラーを返す場合</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>フロント → 外部API</t>
+          <t>フロント</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>GET /files/{fileKey}/url が呼ばれ、署名付きURLからローカルにダウンロードされる</t>
+          <t>アラートが表示される</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>ダウンロードAPI失敗時</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>APIがエラーを返す場合</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>フロント</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>アラートが表示される</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/documents/3_test/02_integration/結合テスト仕様書.xlsx
+++ b/documents/3_test/02_integration/結合テスト仕様書.xlsx
@@ -39,21 +39,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
+      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Yu Gothic"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Yu Gothic"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
@@ -95,7 +100,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -472,11 +477,11 @@
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
-    <col width="8.800000000000001" customWidth="1" min="4" max="4"/>
-    <col width="6.600000000000001" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,7 +491,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -554,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -565,14 +568,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 結合テストでは「画面をまたぐデータ連携」「外部API連携」「E2Eフロー」を確認する</t>
+          <t>・結合テストでは「画面をまたぐデータ連携」「外部API連携」「E2Eフロー」を確認する</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 単画面内で完結するバリデーション・UI制御は単体テスト（01_unit/機能一覧）でカバー済みのため、結合テストには含めない</t>
+          <t>・単画面内で完結するバリデーション・UI制御は単体テスト（01_unit/機能一覧）でカバー済みのため、結合テストには含めない</t>
         </is>
       </c>
     </row>
@@ -788,7 +791,6 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
@@ -899,7 +901,6 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -993,14 +994,14 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="49.50000000000001" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1010,7 +1011,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1070,7 +1070,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -1081,21 +1080,21 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - サイドメニュー年度ドロップダウン変更 → 各一覧画面のデータ再取得 → 表示切り替え</t>
+          <t>・サイドメニュー年度ドロップダウン変更 → 各一覧画面のデータ再取得 → 表示切り替え</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - ロールに応じたサイドメニュー項目の出し分け</t>
+          <t>・ロールに応じたサイドメニュー項目の出し分け</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - サイドメニューから各画面への遷移</t>
+          <t>・サイドメニューから各画面への遷移</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1207,6 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -1408,7 +1406,6 @@
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -1532,14 +1529,14 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="52.8" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1549,7 +1546,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1621,7 +1617,6 @@
       </c>
       <c r="B9" s="4" t="inlineStr"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -1632,21 +1627,21 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 業界CRUD → 行事テンプレートCRUD → エンドユーザー側への反映</t>
+          <t>・業界CRUD → 行事テンプレートCRUD → エンドユーザー側への反映</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 業界大分類・小分類の階層連動</t>
+          <t>・業界大分類・小分類の階層連動</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - デザインテンプレート選択（IT-11で作成したものが選択肢に表示される）</t>
+          <t>・デザインテンプレート選択（IT-11で作成したものが選択肢に表示される）</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1814,6 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -2033,14 +2027,14 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="49.50000000000001" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2050,7 +2044,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2122,7 +2115,6 @@
       </c>
       <c r="B9" s="4" t="inlineStr"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -2133,14 +2125,14 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Brother API連携（GET /source-image-groups → GET /source-image-groups/{id}/source-images）でソース画像を取得</t>
+          <t>・Brother API連携（GET /source-image-groups → GET /source-image-groups/{id}/source-images）でソース画像を取得</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - テンプレートCRUD → 行事テンプレート側（IT-10）の選択肢への反映</t>
+          <t>・テンプレートCRUD → 行事テンプレート側（IT-10）の選択肢への反映</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2305,6 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -2423,7 +2414,6 @@
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -2517,14 +2507,14 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="46.2" customWidth="1" min="3" max="3"/>
-    <col width="15.4" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2534,7 +2524,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2606,7 +2595,6 @@
       </c>
       <c r="B9" s="4" t="inlineStr"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -2617,21 +2605,21 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - ログ管理画面 → 年度/月絞り込み → JavaScript CSV生成 → ダウンロード</t>
+          <t>・ログ管理画面 → 年度/月絞り込み → JavaScript CSV生成 → ダウンロード</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - ダウンロードログCSVと評価ログCSVの2種類が正しく生成されること</t>
+          <t>・ダウンロードログCSVと評価ログCSVの2種類が正しく生成されること</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - リレーション先からの値取得が正しいこと</t>
+          <t>・リレーション先からの値取得が正しいこと</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2732,6 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -2868,14 +2855,14 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="38.5" customWidth="1" min="2" max="2"/>
-    <col width="52.8" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2885,7 +2872,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2957,7 +2943,6 @@
       </c>
       <c r="B9" s="4" t="inlineStr"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -2968,21 +2953,21 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - グループCRUD → 業界紐づけパターンによる配置（全業界共通 / 業界大分類共通 / 業界小分類配下）</t>
+          <t>・グループCRUD → 業界紐づけパターンによる配置（全業界共通 / 業界大分類共通 / 業界小分類配下）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Brother API連携（GET /common-print-groups → GET /common-print-groups/{id}）</t>
+          <t>・Brother API連携（GET /common-print-groups → GET /common-print-groups/{id}）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - エンドユーザー側（IT-07）への反映</t>
+          <t>・エンドユーザー側（IT-07）への反映</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3200,6 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -3325,7 +3309,6 @@
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -3419,14 +3402,14 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3436,7 +3419,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3496,7 +3478,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -3507,14 +3488,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 新規登録 → メール認証 → 企業情報保存 → 初期行事自動作成 → 原稿一覧遷移の一連フロー</t>
+          <t>・新規登録 → メール認証 → 企業情報保存 → 初期行事自動作成 → 原稿一覧遷移の一連フロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 画面間のデータ引き継ぎ（ユーザー情報 → 企業情報 → 行事情報）</t>
+          <t>・画面間のデータ引き継ぎ（ユーザー情報 → 企業情報 → 行事情報）</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3788,6 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -3887,7 +3867,6 @@
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
@@ -4011,14 +3990,14 @@
   <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="35.2" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="52.8" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4028,7 +4007,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4088,7 +4066,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -4099,14 +4076,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 認証API → ロール / 登録状態による遷移先分岐</t>
+          <t>・認証API → ロール / 登録状態による遷移先分岐</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 未ログイン・ロール不一致時の全保護画面アクセス制御</t>
+          <t>・未ログイン・ロール不一致時の全保護画面アクセス制御</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4286,6 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -4419,7 +4395,6 @@
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -4679,7 +4654,6 @@
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
@@ -4863,14 +4837,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
-    <col width="50.6" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4880,7 +4854,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4940,7 +4913,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -4951,14 +4923,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - PW再設定メール送信 → メールのリンク遷移 → PW更新 → 新PWでログイン成功の一連フロー</t>
+          <t>・PW再設定メール送信 → メールのリンク遷移 → PW更新 → 新PWでログイン成功の一連フロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 再設定リンク以外からのアクセス制御</t>
+          <t>・再設定リンク以外からのアクセス制御</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5163,6 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -5315,14 +5286,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
-    <col width="50.6" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5332,7 +5303,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -5392,7 +5362,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -5403,14 +5372,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - PW変更: 旧PW照合API → PW更新API → 新PWでログイン確認</t>
+          <t>・PW変更: 旧PW照合API → PW更新API → 新PWでログイン確認</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - メアド変更: 認証メール送信 → 認証リンク（有効期限あり） → メアド更新 → 新メアドでログイン確認</t>
+          <t>・メアド変更: 認証メール送信 → 認証リンク（有効期限あり） → メアド更新 → 新メアドでログイン確認</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5522,6 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -5767,14 +5735,14 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="40.7" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5784,7 +5752,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -5844,7 +5811,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -5855,14 +5821,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 企業情報保存 → 初期行事情報自動作成 → 原稿一覧への反映</t>
+          <t>・企業情報保存 → 初期行事情報自動作成 → 原稿一覧への反映</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 企業情報編集 → 再表示時にDBの値が反映されること</t>
+          <t>・企業情報編集 → 再表示時にDBの値が反映されること</t>
         </is>
       </c>
     </row>
@@ -6005,7 +5971,6 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -6126,17 +6091,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6146,7 +6111,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -6206,7 +6170,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -6217,21 +6180,21 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 行事保存 → デザイン評価 → Brother API原稿生成 → ポーリング → 原稿表示 → ダウンロードのE2Eフロー</t>
+          <t>・行事保存 → デザイン評価 → Brother API原稿生成 → ポーリング → 原稿表示 → ダウンロードのE2Eフロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Brother API連携（POST /generated-images → GET /generated-images/{id} → GET /files/{fileKey}/url）</t>
+          <t>・Brother API連携（POST /generated-images → GET /generated-images/{id} → GET /files/{fileKey}/url）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 生成対象サイズ: A3・A4・長尺縦・長尺横・ハガキ・封筒（A4便箋はAPI対象外）</t>
+          <t>・生成対象サイズ: A3・A4・長尺縦・長尺横・ハガキ・封筒（A4便箋はAPI対象外）</t>
         </is>
       </c>
     </row>
@@ -6464,225 +6427,283 @@
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ポーリング中にstatus=FAILED</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>生成APIがFAILEDを返す場合</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示されポーリングが終了する</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>IT-06-02 原稿再生成</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>操作ステップ</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>操作内容</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>確認システム</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>実行者</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>実行日</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>再生成実行</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>再生成ボタンを押下する</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>フロント → 外部API</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>POST /generated-images/{id}/regenerate が呼ばれ、ポーリング後に画像が更新される</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>旧データの論理削除確認</t>
+          <t>再生成実行</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>（自動処理）</t>
+          <t>再生成ボタンを押下する</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>バック</t>
+          <t>フロント → 外部API</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>古いus_design_childが論理削除される</t>
+          <t>POST /generated-images/{id}/regenerate が呼ばれ、ポーリング後に画像が更新される</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>旧データの論理削除確認</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>（自動処理）</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>バック</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>古いus_design_childが論理削除される</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>再生成API失敗時</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>APIがエラーを返す場合</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>フロント</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗のアラートが表示される</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>IT-06-03 原稿ダウンロード</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>操作ステップ</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>操作内容</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>確認システム</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>実行者</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>実行日</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>全デザイン評価後にDL</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>全評価完了・DL期限内の状態でDLボタンを押下する</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>フロント → 外部API</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>GET /files/{fileKey}/url が呼ばれ、署名付きURLからダウンロードされる</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ダウンロードAPI失敗時</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>APIがエラーを返す場合</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>フロント</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>アラートが表示される</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6698,14 +6719,14 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="53.90000000000001" customWidth="1" min="1" max="1"/>
-    <col width="55.00000000000001" customWidth="1" min="2" max="2"/>
-    <col width="55.00000000000001" customWidth="1" min="3" max="3"/>
-    <col width="20.9" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6715,7 +6736,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -6775,7 +6795,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -6786,21 +6805,21 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 行事更新 → 再生成API → 画面反映の一連フロー</t>
+          <t>・行事更新 → 再生成API → 画面反映の一連フロー</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 行事複製 → 新規レコード作成 → 一覧反映</t>
+          <t>・行事複製 → 新規レコード作成 → 一覧反映</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 行事削除（論理削除） → 一覧から非表示</t>
+          <t>・行事削除（論理削除） → 一覧から非表示</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6932,6 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -7023,7 +7041,6 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -7147,14 +7164,14 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55.00000000000001" customWidth="1" min="1" max="1"/>
-    <col width="45.1" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55.00000000000001" customWidth="1" min="5" max="5"/>
-    <col width="6.600000000000001" customWidth="1" min="6" max="6"/>
-    <col width="8.800000000000001" customWidth="1" min="7" max="7"/>
-    <col width="8.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7164,7 +7181,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7240,6 @@
       </c>
       <c r="B8" s="4" t="inlineStr"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -7235,14 +7250,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 業界（大分類・小分類）によるグループ表示制御</t>
+          <t>・業界（大分類・小分類）によるグループ表示制御</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - グループ選択 → 印刷物一覧表示 → Brother API（GET /files/{fileKey}/url）→ ダウンロード</t>
+          <t>・グループ選択 → 印刷物一覧表示 → Brother API（GET /files/{fileKey}/url）→ ダウンロード</t>
         </is>
       </c>
     </row>
